--- a/data/inventories_ei310_monte_carlo.xlsx
+++ b/data/inventories_ei310_monte_carlo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF99B11-A4B0-4936-A753-4617A97C1FED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91428290-4BBD-468B-A070-2CFAFA58C89C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="ammonia" sheetId="15" r:id="rId2"/>
     <sheet name="nitrous_oxide" sheetId="25" r:id="rId3"/>
     <sheet name="hydrogen_peroxide" sheetId="26" r:id="rId4"/>
+    <sheet name="phenol" sheetId="27" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="141">
   <si>
     <t>Activity</t>
   </si>
@@ -430,6 +431,21 @@
   </si>
   <si>
     <t>Nitric acid</t>
+  </si>
+  <si>
+    <t>phenol production, nitrous oxide, fossil</t>
+  </si>
+  <si>
+    <t>Benzene</t>
+  </si>
+  <si>
+    <t>phenol production, nitrous oxide, green</t>
+  </si>
+  <si>
+    <t>phenol production, hydrogen peroxide, fossil</t>
+  </si>
+  <si>
+    <t>phenol production, hydrogen peroxide, green</t>
   </si>
   <si>
     <t>nitrous-oxide-ei310</t>
@@ -918,7 +934,7 @@
         <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="5"/>
@@ -1076,7 +1092,7 @@
         <v>3</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -1099,7 +1115,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -1122,7 +1138,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -1145,7 +1161,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -1168,7 +1184,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -1323,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H25" t="s">
         <v>14</v>
@@ -1346,7 +1362,7 @@
         <v>3</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -1369,7 +1385,7 @@
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -1392,7 +1408,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -1415,7 +1431,7 @@
         <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -1438,7 +1454,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -1461,7 +1477,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -1484,7 +1500,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -1507,7 +1523,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -1530,7 +1546,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -1553,7 +1569,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -1576,7 +1592,7 @@
         <v>3</v>
       </c>
       <c r="G36" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -1599,7 +1615,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -1622,7 +1638,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -1645,7 +1661,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
@@ -1668,7 +1684,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -1691,7 +1707,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
@@ -1886,7 +1902,7 @@
         <v>3</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H53" t="s">
         <v>14</v>
@@ -1909,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
@@ -1932,7 +1948,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
@@ -1955,7 +1971,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
@@ -1978,7 +1994,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -2001,7 +2017,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -2024,7 +2040,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -2047,7 +2063,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H60" t="s">
         <v>16</v>
@@ -2070,7 +2086,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H61" t="s">
         <v>16</v>
@@ -2093,7 +2109,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H62" t="s">
         <v>16</v>
@@ -2259,7 +2275,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -2282,7 +2298,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -2305,7 +2321,7 @@
         <v>3</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -2329,7 +2345,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -2352,7 +2368,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -2375,7 +2391,7 @@
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -2398,7 +2414,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -2421,7 +2437,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -2678,7 +2694,7 @@
         <v>3</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>14</v>
@@ -2702,7 +2718,7 @@
         <v>3</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -2725,7 +2741,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -2902,7 +2918,7 @@
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H44" t="s">
         <v>14</v>
@@ -2925,7 +2941,7 @@
         <v>3</v>
       </c>
       <c r="G45" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
@@ -2948,7 +2964,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
@@ -2971,7 +2987,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
@@ -2994,7 +3010,7 @@
         <v>3</v>
       </c>
       <c r="G48" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
@@ -3150,7 +3166,7 @@
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H58" t="s">
         <v>14</v>
@@ -3174,7 +3190,7 @@
         <v>3</v>
       </c>
       <c r="G59" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -3401,7 +3417,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -3424,7 +3440,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -3447,7 +3463,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -3470,7 +3486,7 @@
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -3493,7 +3509,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -3646,7 +3662,7 @@
         <v>3</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H23" t="s">
         <v>14</v>
@@ -3669,7 +3685,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -3692,7 +3708,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -3715,7 +3731,7 @@
         <v>3</v>
       </c>
       <c r="G26" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -3738,7 +3754,7 @@
         <v>3</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -3891,7 +3907,7 @@
         <v>3</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H37" t="s">
         <v>14</v>
@@ -3914,7 +3930,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -3937,7 +3953,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
@@ -3960,7 +3976,7 @@
         <v>3</v>
       </c>
       <c r="G40" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -3983,7 +3999,7 @@
         <v>3</v>
       </c>
       <c r="G41" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
@@ -4006,7 +4022,7 @@
         <v>3</v>
       </c>
       <c r="G42" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -4029,7 +4045,7 @@
         <v>111</v>
       </c>
       <c r="G43" s="21" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
@@ -4242,7 +4258,7 @@
         <v>3</v>
       </c>
       <c r="G56" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H56" t="s">
         <v>14</v>
@@ -4265,7 +4281,7 @@
         <v>3</v>
       </c>
       <c r="G57" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -4288,7 +4304,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -4311,7 +4327,7 @@
         <v>3</v>
       </c>
       <c r="G59" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -4334,7 +4350,7 @@
         <v>3</v>
       </c>
       <c r="G60" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H60" t="s">
         <v>16</v>
@@ -4357,7 +4373,7 @@
         <v>3</v>
       </c>
       <c r="G61" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H61" t="s">
         <v>16</v>
@@ -4380,7 +4396,7 @@
         <v>111</v>
       </c>
       <c r="G62" s="21" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H62" t="s">
         <v>16</v>
@@ -4593,7 +4609,7 @@
         <v>3</v>
       </c>
       <c r="G75" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H75" t="s">
         <v>14</v>
@@ -4616,7 +4632,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H76" t="s">
         <v>16</v>
@@ -4639,7 +4655,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H77" t="s">
         <v>16</v>
@@ -4662,7 +4678,7 @@
         <v>3</v>
       </c>
       <c r="G78" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H78" t="s">
         <v>16</v>
@@ -4685,7 +4701,7 @@
         <v>3</v>
       </c>
       <c r="G79" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H79" t="s">
         <v>16</v>
@@ -4708,7 +4724,7 @@
         <v>3</v>
       </c>
       <c r="G80" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H80" t="s">
         <v>16</v>
@@ -4731,7 +4747,7 @@
         <v>111</v>
       </c>
       <c r="G81" s="21" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H81" t="s">
         <v>16</v>
@@ -4964,7 +4980,7 @@
         <v>3</v>
       </c>
       <c r="G95" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H95" t="s">
         <v>14</v>
@@ -4987,7 +5003,7 @@
         <v>3</v>
       </c>
       <c r="G96" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H96" t="s">
         <v>16</v>
@@ -5010,7 +5026,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H97" t="s">
         <v>16</v>
@@ -5033,7 +5049,7 @@
         <v>3</v>
       </c>
       <c r="G98" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H98" t="s">
         <v>16</v>
@@ -5056,7 +5072,7 @@
         <v>3</v>
       </c>
       <c r="G99" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H99" t="s">
         <v>16</v>
@@ -5079,7 +5095,7 @@
         <v>3</v>
       </c>
       <c r="G100" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H100" t="s">
         <v>16</v>
@@ -5102,7 +5118,7 @@
         <v>111</v>
       </c>
       <c r="G101" s="21" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H101" t="s">
         <v>16</v>
@@ -5335,7 +5351,7 @@
         <v>3</v>
       </c>
       <c r="G115" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H115" t="s">
         <v>14</v>
@@ -5358,7 +5374,7 @@
         <v>15</v>
       </c>
       <c r="G116" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H116" t="s">
         <v>16</v>
@@ -5381,7 +5397,7 @@
         <v>15</v>
       </c>
       <c r="G117" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H117" t="s">
         <v>16</v>
@@ -5404,7 +5420,7 @@
         <v>3</v>
       </c>
       <c r="G118" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H118" t="s">
         <v>16</v>
@@ -5427,7 +5443,7 @@
         <v>3</v>
       </c>
       <c r="G119" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H119" t="s">
         <v>16</v>
@@ -5450,7 +5466,7 @@
         <v>3</v>
       </c>
       <c r="G120" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H120" t="s">
         <v>16</v>
@@ -5473,7 +5489,7 @@
         <v>111</v>
       </c>
       <c r="G121" s="21" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H121" t="s">
         <v>16</v>
@@ -5496,7 +5512,7 @@
         <v>15</v>
       </c>
       <c r="G122" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H122" t="s">
         <v>16</v>
@@ -5709,7 +5725,7 @@
         <v>3</v>
       </c>
       <c r="G135" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H135" t="s">
         <v>14</v>
@@ -5732,7 +5748,7 @@
         <v>3</v>
       </c>
       <c r="G136" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H136" t="s">
         <v>16</v>
@@ -5755,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="G137" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H137" t="s">
         <v>16</v>
@@ -5778,7 +5794,7 @@
         <v>3</v>
       </c>
       <c r="G138" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H138" t="s">
         <v>16</v>
@@ -5801,7 +5817,7 @@
         <v>3</v>
       </c>
       <c r="G139" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H139" t="s">
         <v>16</v>
@@ -5824,7 +5840,7 @@
         <v>3</v>
       </c>
       <c r="G140" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H140" t="s">
         <v>16</v>
@@ -5847,7 +5863,7 @@
         <v>111</v>
       </c>
       <c r="G141" s="21" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H141" t="s">
         <v>16</v>
@@ -5870,7 +5886,7 @@
         <v>15</v>
       </c>
       <c r="G142" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H142" t="s">
         <v>16</v>
@@ -6094,7 +6110,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -6117,7 +6133,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -6140,7 +6156,7 @@
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -6163,7 +6179,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -6186,7 +6202,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -6209,7 +6225,7 @@
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -6232,7 +6248,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -6255,7 +6271,7 @@
         <v>3</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -6278,7 +6294,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
@@ -6493,7 +6509,7 @@
         <v>3</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H30" t="s">
         <v>14</v>
@@ -6516,7 +6532,7 @@
         <v>3</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -6539,7 +6555,7 @@
         <v>3</v>
       </c>
       <c r="G32" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -6562,7 +6578,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -6585,7 +6601,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -6608,7 +6624,7 @@
         <v>3</v>
       </c>
       <c r="G35" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -6631,7 +6647,7 @@
         <v>3</v>
       </c>
       <c r="G36" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -6654,7 +6670,7 @@
         <v>3</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -6677,7 +6693,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -6749,4 +6765,1252 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{150773DC-8801-4506-8832-5BE54A26FACF}">
+  <dimension ref="A1:H67"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="9">
+        <v>1</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" s="11">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="24">
+        <v>0.82850000000000001</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="24">
+        <v>0.4753</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="24">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0.97905439999999999</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="11">
+        <v>12.783581</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>140</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="11">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="13">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="11">
+        <v>0.30220000000000002</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="9">
+        <v>1</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="11">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C28" s="24">
+        <v>0.82850000000000001</v>
+      </c>
+      <c r="D28" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s">
+        <v>140</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="24">
+        <v>0.4753</v>
+      </c>
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" t="s">
+        <v>139</v>
+      </c>
+      <c r="H29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="24">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" t="s">
+        <v>3</v>
+      </c>
+      <c r="G30" t="s">
+        <v>140</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="11">
+        <v>0.97905439999999999</v>
+      </c>
+      <c r="D31" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="11">
+        <v>12.783581</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s">
+        <v>140</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>135</v>
+      </c>
+      <c r="C33" s="11">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" t="s">
+        <v>102</v>
+      </c>
+      <c r="H33" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="13">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="11">
+        <v>0.30220000000000002</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C37" s="16"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="16"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="9">
+        <v>1</v>
+      </c>
+      <c r="C40" s="16"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" s="16"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="16"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>137</v>
+      </c>
+      <c r="B45" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" s="11">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>118</v>
+      </c>
+      <c r="B46" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" s="24">
+        <v>0.92220000000000002</v>
+      </c>
+      <c r="D46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s">
+        <v>140</v>
+      </c>
+      <c r="H46" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" s="24">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="D47" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" t="s">
+        <v>139</v>
+      </c>
+      <c r="H47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" s="24">
+        <v>0</v>
+      </c>
+      <c r="D48" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H48" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="11">
+        <v>4.9474215120689138</v>
+      </c>
+      <c r="D49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H49" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50" s="11">
+        <v>6.9231678675119195</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s">
+        <v>140</v>
+      </c>
+      <c r="H50" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>89</v>
+      </c>
+      <c r="B51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="13">
+        <v>-2.7E-4</v>
+      </c>
+      <c r="D51" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s">
+        <v>140</v>
+      </c>
+      <c r="H51" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C53" s="16"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="16"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="9">
+        <v>1</v>
+      </c>
+      <c r="C56" s="16"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C57" s="16"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="16"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" s="3"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" t="s">
+        <v>138</v>
+      </c>
+      <c r="C61" s="11">
+        <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" t="s">
+        <v>3</v>
+      </c>
+      <c r="G61" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H61" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>118</v>
+      </c>
+      <c r="B62" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="24">
+        <v>0.92220000000000002</v>
+      </c>
+      <c r="D62" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s">
+        <v>140</v>
+      </c>
+      <c r="H62" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>120</v>
+      </c>
+      <c r="B63" t="s">
+        <v>120</v>
+      </c>
+      <c r="C63" s="24">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" t="s">
+        <v>3</v>
+      </c>
+      <c r="G63" t="s">
+        <v>139</v>
+      </c>
+      <c r="H63" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64" t="s">
+        <v>34</v>
+      </c>
+      <c r="C64" s="24">
+        <v>0</v>
+      </c>
+      <c r="D64" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" t="s">
+        <v>3</v>
+      </c>
+      <c r="G64" t="s">
+        <v>140</v>
+      </c>
+      <c r="H64" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>99</v>
+      </c>
+      <c r="B65" t="s">
+        <v>99</v>
+      </c>
+      <c r="C65" s="11">
+        <v>4.9474215120689138</v>
+      </c>
+      <c r="D65" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" t="s">
+        <v>3</v>
+      </c>
+      <c r="G65" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H65" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" t="s">
+        <v>36</v>
+      </c>
+      <c r="C66" s="11">
+        <v>6.9231678675119195</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s">
+        <v>140</v>
+      </c>
+      <c r="H66" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>89</v>
+      </c>
+      <c r="B67" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" s="13">
+        <v>-2.7E-4</v>
+      </c>
+      <c r="D67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s">
+        <v>140</v>
+      </c>
+      <c r="H67" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/inventories_ei310_monte_carlo.xlsx
+++ b/data/inventories_ei310_monte_carlo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91428290-4BBD-468B-A070-2CFAFA58C89C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBF6600-3E81-4EF8-93F7-AFA4AFB67F0C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" activeTab="3" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="hydrogen" sheetId="14" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="144">
   <si>
     <t>Activity</t>
   </si>
@@ -452,6 +452,15 @@
   </si>
   <si>
     <t>ecoinvent-3.10-cutoff</t>
+  </si>
+  <si>
+    <t>uncertainty type</t>
+  </si>
+  <si>
+    <t>loc</t>
+  </si>
+  <si>
+    <t>scale</t>
   </si>
 </sst>
 </file>
@@ -540,7 +549,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -598,6 +607,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -916,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19992C32-C4F6-41C6-855E-97A9929F367E}">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="101.140625" bestFit="1" customWidth="1"/>
@@ -927,9 +939,12 @@
     <col min="6" max="6" width="36.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>23</v>
       </c>
@@ -942,8 +957,11 @@
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="17"/>
@@ -952,8 +970,11 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -967,7 +988,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -981,7 +1002,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -995,7 +1016,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -1009,7 +1030,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -1023,7 +1044,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -1037,7 +1058,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1049,7 +1070,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>5</v>
       </c>
@@ -1074,8 +1095,17 @@
       <c r="H10" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>141</v>
+      </c>
+      <c r="J10" t="s">
+        <v>142</v>
+      </c>
+      <c r="K10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>104</v>
       </c>
@@ -1098,7 +1128,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1120,8 +1150,19 @@
       <c r="H12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="10">
+        <v>3</v>
+      </c>
+      <c r="J12" s="12">
+        <f>C12</f>
+        <v>1</v>
+      </c>
+      <c r="K12" s="12">
+        <f>0.1*J12</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>78</v>
       </c>
@@ -1143,8 +1184,19 @@
       <c r="H13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="10">
+        <v>3</v>
+      </c>
+      <c r="J13" s="12">
+        <f t="shared" ref="J13:J15" si="0">C13</f>
+        <v>9</v>
+      </c>
+      <c r="K13" s="12">
+        <f t="shared" ref="K13:K15" si="1">0.1*J13</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
@@ -1166,8 +1218,19 @@
       <c r="H14" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="10">
+        <v>3</v>
+      </c>
+      <c r="J14" s="12">
+        <f t="shared" si="0"/>
+        <v>0.18</v>
+      </c>
+      <c r="K14" s="12">
+        <f t="shared" si="1"/>
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1189,8 +1252,19 @@
       <c r="H15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="10">
+        <v>3</v>
+      </c>
+      <c r="J15" s="12">
+        <f t="shared" si="0"/>
+        <v>55.05681818181818</v>
+      </c>
+      <c r="K15" s="12">
+        <f t="shared" si="1"/>
+        <v>5.5056818181818183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="17"/>
@@ -1199,8 +1273,11 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -1214,7 +1291,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>1</v>
       </c>
@@ -1228,7 +1305,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>2</v>
       </c>
@@ -1242,7 +1319,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1256,7 +1333,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1270,7 +1347,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -1284,7 +1361,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
@@ -1296,7 +1373,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>5</v>
       </c>
@@ -1321,8 +1398,17 @@
       <c r="H24" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" t="s">
+        <v>141</v>
+      </c>
+      <c r="J24" t="s">
+        <v>142</v>
+      </c>
+      <c r="K24" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1345,7 +1431,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -1367,8 +1453,11 @@
       <c r="H26" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" s="10"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>71</v>
       </c>
@@ -1390,8 +1479,11 @@
       <c r="H27" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" s="10"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>73</v>
       </c>
@@ -1413,8 +1505,11 @@
       <c r="H28" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" s="10"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>74</v>
       </c>
@@ -1436,8 +1531,11 @@
       <c r="H29" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="10"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>75</v>
       </c>
@@ -1459,8 +1557,11 @@
       <c r="H30" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="10"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>43</v>
       </c>
@@ -1482,8 +1583,11 @@
       <c r="H31" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="10"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
@@ -1505,8 +1609,11 @@
       <c r="H32" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="10"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>76</v>
       </c>
@@ -1528,8 +1635,11 @@
       <c r="H33" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="10"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>77</v>
       </c>
@@ -1551,8 +1661,11 @@
       <c r="H34" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="10"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="13"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>78</v>
       </c>
@@ -1574,8 +1687,19 @@
       <c r="H35" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="10">
+        <v>3</v>
+      </c>
+      <c r="J35" s="12">
+        <f t="shared" ref="J35:J37" si="2">C35</f>
+        <v>9.4500000000000001E-3</v>
+      </c>
+      <c r="K35" s="12">
+        <f>0.1*J35</f>
+        <v>9.4500000000000009E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -1597,8 +1721,11 @@
       <c r="H36" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36" s="10"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="13"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
@@ -1620,8 +1747,19 @@
       <c r="H37" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37" s="10">
+        <v>3</v>
+      </c>
+      <c r="J37" s="12">
+        <f t="shared" si="2"/>
+        <v>9.7199999999999995E-3</v>
+      </c>
+      <c r="K37" s="12">
+        <f>0.1*J37</f>
+        <v>9.7199999999999999E-4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>79</v>
       </c>
@@ -1643,8 +1781,11 @@
       <c r="H38" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38" s="10"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>80</v>
       </c>
@@ -1666,8 +1807,11 @@
       <c r="H39" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" s="10"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>69</v>
       </c>
@@ -1689,8 +1833,11 @@
       <c r="H40" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" s="10"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>70</v>
       </c>
@@ -1712,8 +1859,11 @@
       <c r="H41" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41" s="10"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>81</v>
       </c>
@@ -1733,7 +1883,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>82</v>
       </c>
@@ -1753,7 +1903,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="17"/>
@@ -1762,8 +1912,11 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>0</v>
       </c>
@@ -1777,7 +1930,7 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>1</v>
       </c>
@@ -1791,7 +1944,7 @@
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>2</v>
       </c>
@@ -1805,7 +1958,7 @@
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>4</v>
       </c>
@@ -1819,7 +1972,7 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>5</v>
       </c>
@@ -1833,7 +1986,7 @@
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>6</v>
       </c>
@@ -1847,7 +2000,7 @@
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>8</v>
       </c>
@@ -1859,7 +2012,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>5</v>
       </c>
@@ -1884,8 +2037,17 @@
       <c r="H52" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I52" t="s">
+        <v>141</v>
+      </c>
+      <c r="J52" t="s">
+        <v>142</v>
+      </c>
+      <c r="K52" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>41</v>
       </c>
@@ -1908,7 +2070,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>43</v>
       </c>
@@ -1930,8 +2092,19 @@
       <c r="H54" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I54" s="10">
+        <v>3</v>
+      </c>
+      <c r="J54" s="12">
+        <f t="shared" ref="J54:J61" si="3">C54</f>
+        <v>7.6300000000000007E-2</v>
+      </c>
+      <c r="K54" s="12">
+        <f t="shared" ref="K54:K61" si="4">0.1*J54</f>
+        <v>7.6300000000000014E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>44</v>
       </c>
@@ -1953,8 +2126,19 @@
       <c r="H55" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I55" s="10">
+        <v>3</v>
+      </c>
+      <c r="J55" s="12">
+        <f t="shared" si="3"/>
+        <v>0.156</v>
+      </c>
+      <c r="K55" s="12">
+        <f t="shared" si="4"/>
+        <v>1.5600000000000001E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>45</v>
       </c>
@@ -1976,8 +2160,19 @@
       <c r="H56" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I56" s="10">
+        <v>3</v>
+      </c>
+      <c r="J56" s="12">
+        <f t="shared" si="3"/>
+        <v>4.7899999999999998E-2</v>
+      </c>
+      <c r="K56" s="12">
+        <f t="shared" si="4"/>
+        <v>4.79E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>46</v>
       </c>
@@ -1999,8 +2194,19 @@
       <c r="H57" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I57" s="10">
+        <v>3</v>
+      </c>
+      <c r="J57" s="12">
+        <f t="shared" si="3"/>
+        <v>5.28E-2</v>
+      </c>
+      <c r="K57" s="12">
+        <f t="shared" si="4"/>
+        <v>5.28E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>47</v>
       </c>
@@ -2022,8 +2228,19 @@
       <c r="H58" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I58" s="10">
+        <v>3</v>
+      </c>
+      <c r="J58" s="12">
+        <f t="shared" si="3"/>
+        <v>8.6099999999999996E-2</v>
+      </c>
+      <c r="K58" s="12">
+        <f t="shared" si="4"/>
+        <v>8.6099999999999996E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>48</v>
       </c>
@@ -2045,8 +2262,19 @@
       <c r="H59" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I59" s="10">
+        <v>3</v>
+      </c>
+      <c r="J59" s="12">
+        <f t="shared" si="3"/>
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="K59" s="12">
+        <f t="shared" si="4"/>
+        <v>3.2300000000000002E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>49</v>
       </c>
@@ -2068,8 +2296,19 @@
       <c r="H60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I60" s="10">
+        <v>3</v>
+      </c>
+      <c r="J60" s="12">
+        <f t="shared" si="3"/>
+        <v>0.127</v>
+      </c>
+      <c r="K60" s="12">
+        <f t="shared" si="4"/>
+        <v>1.2700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -2091,8 +2330,19 @@
       <c r="H61" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I61" s="10">
+        <v>3</v>
+      </c>
+      <c r="J61" s="12">
+        <f t="shared" si="3"/>
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="K61" s="12">
+        <f t="shared" si="4"/>
+        <v>4.2099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>32</v>
       </c>
@@ -2114,6 +2364,24 @@
       <c r="H62" t="s">
         <v>16</v>
       </c>
+      <c r="I62" s="10"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K63" s="25"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K64" s="25"/>
+    </row>
+    <row r="65" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K65" s="25"/>
+    </row>
+    <row r="66" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K66" s="25"/>
+    </row>
+    <row r="67" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K67" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2123,12 +2391,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32C298A7-421E-4EE1-B228-96CCD2740E23}">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="101.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="100.28515625" customWidth="1"/>
-    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="34.28515625" bestFit="1" customWidth="1"/>
@@ -2136,7 +2404,7 @@
     <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2150,7 +2418,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2164,7 +2432,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2178,7 +2446,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -2192,7 +2460,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -2206,7 +2474,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
@@ -2220,7 +2488,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -2232,7 +2500,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
@@ -2257,8 +2525,17 @@
       <c r="H8" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" t="s">
+        <v>141</v>
+      </c>
+      <c r="J8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>105</v>
       </c>
@@ -2281,7 +2558,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>97</v>
       </c>
@@ -2303,8 +2580,19 @@
       <c r="H10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="10">
+        <v>3</v>
+      </c>
+      <c r="J10" s="12">
+        <f>C10</f>
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="K10" s="12">
+        <f>0.1*J10</f>
+        <v>8.1500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -2326,8 +2614,11 @@
       <c r="H11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="10"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>99</v>
       </c>
@@ -2350,8 +2641,19 @@
       <c r="H12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="10">
+        <v>3</v>
+      </c>
+      <c r="J12" s="12">
+        <f t="shared" ref="J12:J15" si="0">C12</f>
+        <v>9.3467699999999994</v>
+      </c>
+      <c r="K12" s="12">
+        <f>0.1*J12</f>
+        <v>0.93467699999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>104</v>
       </c>
@@ -2373,8 +2675,19 @@
       <c r="H13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="10">
+        <v>3</v>
+      </c>
+      <c r="J13" s="12">
+        <f t="shared" si="0"/>
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="K13" s="12">
+        <f>0.1*J13</f>
+        <v>1.7600000000000001E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -2396,8 +2709,11 @@
       <c r="H14" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="10"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -2419,8 +2735,19 @@
       <c r="H15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="10">
+        <v>3</v>
+      </c>
+      <c r="J15" s="12">
+        <f t="shared" si="0"/>
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="K15" s="12">
+        <f>0.1*J15</f>
+        <v>5.5600000000000011E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -2442,8 +2769,11 @@
       <c r="H16" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" s="10"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>90</v>
       </c>
@@ -2463,7 +2793,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>39</v>
       </c>
@@ -2483,7 +2813,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>21</v>
       </c>
@@ -2503,7 +2833,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>86</v>
       </c>
@@ -2524,7 +2854,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>86</v>
       </c>
@@ -2545,7 +2875,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="17"/>
@@ -2554,8 +2884,11 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -2569,7 +2902,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>1</v>
       </c>
@@ -2583,7 +2916,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>2</v>
       </c>
@@ -2597,7 +2930,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>4</v>
       </c>
@@ -2611,7 +2944,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>5</v>
       </c>
@@ -2625,7 +2958,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>6</v>
       </c>
@@ -2639,7 +2972,7 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>8</v>
       </c>
@@ -2651,7 +2984,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>5</v>
       </c>
@@ -2676,8 +3009,17 @@
       <c r="H30" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" t="s">
+        <v>141</v>
+      </c>
+      <c r="J30" t="s">
+        <v>142</v>
+      </c>
+      <c r="K30" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>97</v>
       </c>
@@ -2700,7 +3042,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>99</v>
       </c>
@@ -2723,8 +3065,19 @@
       <c r="H32" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="10">
+        <v>3</v>
+      </c>
+      <c r="J32" s="12">
+        <f>C32</f>
+        <v>0.25091999999999998</v>
+      </c>
+      <c r="K32" s="12">
+        <f>0.1*J32</f>
+        <v>2.5092E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>96</v>
       </c>
@@ -2746,8 +3099,11 @@
       <c r="H33" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="10"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B34" s="14" t="s">
         <v>86</v>
       </c>
@@ -2768,7 +3124,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="17"/>
@@ -2777,8 +3133,11 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
@@ -2792,7 +3151,7 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>1</v>
       </c>
@@ -2806,7 +3165,7 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>2</v>
       </c>
@@ -2820,7 +3179,7 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>4</v>
       </c>
@@ -2834,7 +3193,7 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>5</v>
       </c>
@@ -2848,7 +3207,7 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>6</v>
       </c>
@@ -2862,7 +3221,7 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>8</v>
       </c>
@@ -2874,7 +3233,7 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>5</v>
       </c>
@@ -2899,8 +3258,17 @@
       <c r="H43" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" t="s">
+        <v>141</v>
+      </c>
+      <c r="J43" t="s">
+        <v>142</v>
+      </c>
+      <c r="K43" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>91</v>
       </c>
@@ -2924,7 +3292,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>84</v>
       </c>
@@ -2946,8 +3314,19 @@
       <c r="H45" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I45" s="10">
+        <v>3</v>
+      </c>
+      <c r="J45" s="12">
+        <f>C45</f>
+        <v>0.97099999999999997</v>
+      </c>
+      <c r="K45" s="12">
+        <f>0.1*J45</f>
+        <v>9.7100000000000006E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -2969,8 +3348,19 @@
       <c r="H46" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I46" s="10">
+        <v>3</v>
+      </c>
+      <c r="J46" s="12">
+        <f t="shared" ref="J46:J48" si="1">C46</f>
+        <v>0.03</v>
+      </c>
+      <c r="K46" s="12">
+        <f>0.1*J46</f>
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -2992,8 +3382,19 @@
       <c r="H47" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47" s="10">
+        <v>3</v>
+      </c>
+      <c r="J47" s="12">
+        <f t="shared" si="1"/>
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="K47" s="12">
+        <f>0.1*J47</f>
+        <v>5.2500000000000003E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>33</v>
       </c>
@@ -3015,8 +3416,19 @@
       <c r="H48" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48" s="10">
+        <v>3</v>
+      </c>
+      <c r="J48" s="12">
+        <f t="shared" si="1"/>
+        <v>1.78</v>
+      </c>
+      <c r="K48" s="12">
+        <f>0.1*J48</f>
+        <v>0.17800000000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="17"/>
@@ -3025,8 +3437,11 @@
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>0</v>
       </c>
@@ -3040,7 +3455,7 @@
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>1</v>
       </c>
@@ -3054,7 +3469,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>2</v>
       </c>
@@ -3068,7 +3483,7 @@
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>4</v>
       </c>
@@ -3082,7 +3497,7 @@
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3096,7 +3511,7 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>6</v>
       </c>
@@ -3110,7 +3525,7 @@
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>8</v>
       </c>
@@ -3122,7 +3537,7 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>5</v>
       </c>
@@ -3147,8 +3562,17 @@
       <c r="H57" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I57" t="s">
+        <v>141</v>
+      </c>
+      <c r="J57" t="s">
+        <v>142</v>
+      </c>
+      <c r="K57" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>99</v>
       </c>
@@ -3172,7 +3596,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>33</v>
       </c>
@@ -3195,8 +3619,11 @@
       <c r="H59" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I59" s="10"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>86</v>
       </c>
@@ -3216,8 +3643,9 @@
       <c r="H60" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K60" s="25"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>86</v>
       </c>
@@ -3238,7 +3666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>20</v>
       </c>
@@ -3267,7 +3695,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A007D5B7-6BDB-4C5E-BE6E-870683E782C1}">
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:K145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.5703125" bestFit="1" customWidth="1"/>
@@ -3280,7 +3708,7 @@
     <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3294,7 +3722,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3306,7 +3734,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -3320,7 +3748,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -3334,7 +3762,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -3348,7 +3776,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
@@ -3362,7 +3790,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -3374,7 +3802,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
@@ -3399,8 +3827,17 @@
       <c r="H8" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" t="s">
+        <v>141</v>
+      </c>
+      <c r="J8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>119</v>
       </c>
@@ -3423,7 +3860,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>107</v>
       </c>
@@ -3445,8 +3882,19 @@
       <c r="H10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="10">
+        <v>3</v>
+      </c>
+      <c r="J10" s="12">
+        <f>C10</f>
+        <v>0.81841179834052924</v>
+      </c>
+      <c r="K10" s="12">
+        <f>0.1*J10</f>
+        <v>8.1841179834052924E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>89</v>
       </c>
@@ -3468,8 +3916,11 @@
       <c r="H11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="10"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -3491,8 +3942,19 @@
       <c r="H12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="10">
+        <v>3</v>
+      </c>
+      <c r="J12" s="12">
+        <f t="shared" ref="J12:J13" si="0">C12</f>
+        <v>5.0274871051467697E-2</v>
+      </c>
+      <c r="K12" s="12">
+        <f>0.1*J12</f>
+        <v>5.0274871051467704E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>99</v>
       </c>
@@ -3514,8 +3976,19 @@
       <c r="H13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="10">
+        <v>3</v>
+      </c>
+      <c r="J13" s="12">
+        <f t="shared" si="0"/>
+        <v>4.5210811907473172</v>
+      </c>
+      <c r="K13" s="12">
+        <f>0.1*J13</f>
+        <v>0.45210811907473175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="17"/>
@@ -3524,8 +3997,11 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -3539,7 +4015,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>1</v>
       </c>
@@ -3551,7 +4027,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
@@ -3565,7 +4041,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
@@ -3579,7 +4055,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>5</v>
       </c>
@@ -3593,7 +4069,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>6</v>
       </c>
@@ -3607,7 +4083,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>8</v>
       </c>
@@ -3619,7 +4095,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>5</v>
       </c>
@@ -3644,8 +4120,17 @@
       <c r="H22" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I22" t="s">
+        <v>141</v>
+      </c>
+      <c r="J22" t="s">
+        <v>142</v>
+      </c>
+      <c r="K22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>122</v>
       </c>
@@ -3668,7 +4153,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>105</v>
       </c>
@@ -3690,8 +4175,19 @@
       <c r="H24" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" s="10">
+        <v>3</v>
+      </c>
+      <c r="J24" s="12">
+        <f>C24</f>
+        <v>0.81841179834052924</v>
+      </c>
+      <c r="K24" s="12">
+        <f>0.1*J24</f>
+        <v>8.1841179834052924E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>89</v>
       </c>
@@ -3713,8 +4209,11 @@
       <c r="H25" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" s="10"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3736,8 +4235,19 @@
       <c r="H26" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" s="10">
+        <v>3</v>
+      </c>
+      <c r="J26" s="12">
+        <f t="shared" ref="J26:J27" si="1">C26</f>
+        <v>5.0274871051467697E-2</v>
+      </c>
+      <c r="K26" s="12">
+        <f>0.1*J26</f>
+        <v>5.0274871051467704E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>99</v>
       </c>
@@ -3759,8 +4269,19 @@
       <c r="H27" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" s="10">
+        <v>3</v>
+      </c>
+      <c r="J27" s="12">
+        <f t="shared" si="1"/>
+        <v>4.5210811907473172</v>
+      </c>
+      <c r="K27" s="12">
+        <f>0.1*J27</f>
+        <v>0.45210811907473175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="17"/>
@@ -3769,8 +4290,11 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -3784,7 +4308,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>1</v>
       </c>
@@ -3796,7 +4320,7 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>2</v>
       </c>
@@ -3810,7 +4334,7 @@
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>4</v>
       </c>
@@ -3824,7 +4348,7 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>5</v>
       </c>
@@ -3838,7 +4362,7 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>6</v>
       </c>
@@ -3852,7 +4376,7 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>8</v>
       </c>
@@ -3864,7 +4388,7 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>5</v>
       </c>
@@ -3889,8 +4413,17 @@
       <c r="H36" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36" t="s">
+        <v>141</v>
+      </c>
+      <c r="J36" t="s">
+        <v>142</v>
+      </c>
+      <c r="K36" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>129</v>
       </c>
@@ -3913,7 +4446,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>107</v>
       </c>
@@ -3935,8 +4468,19 @@
       <c r="H38" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38" s="10">
+        <v>3</v>
+      </c>
+      <c r="J38" s="12">
+        <f>C38</f>
+        <v>0.90659390280881114</v>
+      </c>
+      <c r="K38" s="12">
+        <f>0.1*J38</f>
+        <v>9.0659390280881116E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>89</v>
       </c>
@@ -3958,8 +4502,11 @@
       <c r="H39" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" s="10"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -3981,8 +4528,11 @@
       <c r="H40" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" s="10"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -4004,8 +4554,19 @@
       <c r="H41" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41" s="10">
+        <v>3</v>
+      </c>
+      <c r="J41" s="12">
+        <f t="shared" ref="J41:J43" si="2">C41</f>
+        <v>5.9409513565910815E-2</v>
+      </c>
+      <c r="K41" s="12">
+        <f>0.1*J41</f>
+        <v>5.9409513565910821E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>99</v>
       </c>
@@ -4027,8 +4588,19 @@
       <c r="H42" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I42" s="10">
+        <v>3</v>
+      </c>
+      <c r="J42" s="12">
+        <f t="shared" si="2"/>
+        <v>4.5997084648075042</v>
+      </c>
+      <c r="K42" s="12">
+        <f>0.1*J42</f>
+        <v>0.45997084648075043</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>109</v>
       </c>
@@ -4050,8 +4622,19 @@
       <c r="H43" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" s="10">
+        <v>3</v>
+      </c>
+      <c r="J43" s="12">
+        <f t="shared" si="2"/>
+        <v>0.59735221660353577</v>
+      </c>
+      <c r="K43" s="12">
+        <f>0.1*J43</f>
+        <v>5.9735221660353582E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>101</v>
       </c>
@@ -4071,7 +4654,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>108</v>
       </c>
@@ -4091,7 +4674,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>21</v>
       </c>
@@ -4111,7 +4694,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="17"/>
@@ -4120,8 +4703,11 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>0</v>
       </c>
@@ -4135,7 +4721,7 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>1</v>
       </c>
@@ -4147,7 +4733,7 @@
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>2</v>
       </c>
@@ -4161,7 +4747,7 @@
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>4</v>
       </c>
@@ -4175,7 +4761,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4189,7 +4775,7 @@
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>6</v>
       </c>
@@ -4203,7 +4789,7 @@
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>8</v>
       </c>
@@ -4215,7 +4801,7 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>5</v>
       </c>
@@ -4240,8 +4826,17 @@
       <c r="H55" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I55" t="s">
+        <v>141</v>
+      </c>
+      <c r="J55" t="s">
+        <v>142</v>
+      </c>
+      <c r="K55" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>130</v>
       </c>
@@ -4264,7 +4859,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>105</v>
       </c>
@@ -4286,8 +4881,19 @@
       <c r="H57" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I57" s="10">
+        <v>3</v>
+      </c>
+      <c r="J57" s="12">
+        <f>C57</f>
+        <v>0.90659390280881114</v>
+      </c>
+      <c r="K57" s="12">
+        <f>0.1*J57</f>
+        <v>9.0659390280881116E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>89</v>
       </c>
@@ -4309,8 +4915,11 @@
       <c r="H58" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I58" s="10"/>
+      <c r="J58" s="12"/>
+      <c r="K58" s="12"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>123</v>
       </c>
@@ -4332,8 +4941,11 @@
       <c r="H59" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I59" s="10"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>33</v>
       </c>
@@ -4355,8 +4967,19 @@
       <c r="H60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I60" s="10">
+        <v>3</v>
+      </c>
+      <c r="J60" s="12">
+        <f t="shared" ref="J60:J62" si="3">C60</f>
+        <v>5.9409513565910815E-2</v>
+      </c>
+      <c r="K60" s="12">
+        <f>0.1*J60</f>
+        <v>5.9409513565910821E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>99</v>
       </c>
@@ -4378,8 +5001,19 @@
       <c r="H61" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I61" s="10">
+        <v>3</v>
+      </c>
+      <c r="J61" s="12">
+        <f t="shared" si="3"/>
+        <v>4.5997084648075042</v>
+      </c>
+      <c r="K61" s="12">
+        <f>0.1*J61</f>
+        <v>0.45997084648075043</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>109</v>
       </c>
@@ -4401,8 +5035,19 @@
       <c r="H62" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I62" s="10">
+        <v>3</v>
+      </c>
+      <c r="J62" s="12">
+        <f t="shared" si="3"/>
+        <v>0.59735221660353577</v>
+      </c>
+      <c r="K62" s="12">
+        <f>0.1*J62</f>
+        <v>5.9735221660353582E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>101</v>
       </c>
@@ -4422,7 +5067,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>108</v>
       </c>
@@ -4442,7 +5087,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>21</v>
       </c>
@@ -4462,7 +5107,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="17"/>
@@ -4471,8 +5116,11 @@
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>0</v>
       </c>
@@ -4486,7 +5134,7 @@
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>1</v>
       </c>
@@ -4498,7 +5146,7 @@
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>2</v>
       </c>
@@ -4512,7 +5160,7 @@
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>4</v>
       </c>
@@ -4526,7 +5174,7 @@
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>5</v>
       </c>
@@ -4540,7 +5188,7 @@
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>6</v>
       </c>
@@ -4554,7 +5202,7 @@
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>8</v>
       </c>
@@ -4566,7 +5214,7 @@
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>5</v>
       </c>
@@ -4591,8 +5239,17 @@
       <c r="H74" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I74" t="s">
+        <v>141</v>
+      </c>
+      <c r="J74" t="s">
+        <v>142</v>
+      </c>
+      <c r="K74" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>127</v>
       </c>
@@ -4615,7 +5272,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>107</v>
       </c>
@@ -4637,8 +5294,19 @@
       <c r="H76" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I76" s="10">
+        <v>3</v>
+      </c>
+      <c r="J76" s="12">
+        <f>C76</f>
+        <v>0.9036534629177585</v>
+      </c>
+      <c r="K76" s="12">
+        <f>0.1*J76</f>
+        <v>9.0365346291775853E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>89</v>
       </c>
@@ -4660,8 +5328,11 @@
       <c r="H77" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I77" s="10"/>
+      <c r="J77" s="12"/>
+      <c r="K77" s="12"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>123</v>
       </c>
@@ -4683,8 +5354,11 @@
       <c r="H78" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I78" s="10"/>
+      <c r="J78" s="12"/>
+      <c r="K78" s="12"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>33</v>
       </c>
@@ -4706,8 +5380,19 @@
       <c r="H79" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I79" s="10">
+        <v>3</v>
+      </c>
+      <c r="J79" s="12">
+        <f t="shared" ref="J79:J80" si="4">C79</f>
+        <v>7.9660098771632923E-2</v>
+      </c>
+      <c r="K79" s="12">
+        <f>0.1*J79</f>
+        <v>7.966009877163293E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>99</v>
       </c>
@@ -4729,8 +5414,19 @@
       <c r="H80" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I80" s="10">
+        <v>3</v>
+      </c>
+      <c r="J80" s="12">
+        <f t="shared" si="4"/>
+        <v>5.0729694968067038</v>
+      </c>
+      <c r="K80" s="12">
+        <f>0.1*J80</f>
+        <v>0.50729694968067041</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>109</v>
       </c>
@@ -4752,8 +5448,11 @@
       <c r="H81" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I81" s="10"/>
+      <c r="J81" s="12"/>
+      <c r="K81" s="12"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>101</v>
       </c>
@@ -4773,7 +5472,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>108</v>
       </c>
@@ -4793,7 +5492,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>21</v>
       </c>
@@ -4813,7 +5512,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>86</v>
       </c>
@@ -4833,7 +5532,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="17"/>
@@ -4842,8 +5541,11 @@
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>0</v>
       </c>
@@ -4857,7 +5559,7 @@
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>1</v>
       </c>
@@ -4869,7 +5571,7 @@
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>2</v>
       </c>
@@ -4883,7 +5585,7 @@
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>4</v>
       </c>
@@ -4897,7 +5599,7 @@
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>5</v>
       </c>
@@ -4911,7 +5613,7 @@
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>6</v>
       </c>
@@ -4925,7 +5627,7 @@
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>8</v>
       </c>
@@ -4937,7 +5639,7 @@
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>5</v>
       </c>
@@ -4962,8 +5664,17 @@
       <c r="H94" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I94" t="s">
+        <v>141</v>
+      </c>
+      <c r="J94" t="s">
+        <v>142</v>
+      </c>
+      <c r="K94" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>128</v>
       </c>
@@ -4986,7 +5697,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>105</v>
       </c>
@@ -5008,8 +5719,19 @@
       <c r="H96" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I96" s="10">
+        <v>3</v>
+      </c>
+      <c r="J96" s="12">
+        <f>C96</f>
+        <v>0.9036534629177585</v>
+      </c>
+      <c r="K96" s="12">
+        <f>0.1*J96</f>
+        <v>9.0365346291775853E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>89</v>
       </c>
@@ -5031,8 +5753,11 @@
       <c r="H97" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I97" s="10"/>
+      <c r="J97" s="12"/>
+      <c r="K97" s="12"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>123</v>
       </c>
@@ -5054,8 +5779,11 @@
       <c r="H98" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I98" s="10"/>
+      <c r="J98" s="12"/>
+      <c r="K98" s="12"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>33</v>
       </c>
@@ -5077,8 +5805,19 @@
       <c r="H99" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I99" s="10">
+        <v>3</v>
+      </c>
+      <c r="J99" s="12">
+        <f t="shared" ref="J99:J100" si="5">C99</f>
+        <v>7.9660098771632923E-2</v>
+      </c>
+      <c r="K99" s="12">
+        <f>0.1*J99</f>
+        <v>7.966009877163293E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -5100,8 +5839,19 @@
       <c r="H100" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I100" s="10">
+        <v>3</v>
+      </c>
+      <c r="J100" s="12">
+        <f t="shared" si="5"/>
+        <v>5.0729694968067038</v>
+      </c>
+      <c r="K100" s="12">
+        <f>0.1*J100</f>
+        <v>0.50729694968067041</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>109</v>
       </c>
@@ -5123,8 +5873,11 @@
       <c r="H101" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I101" s="10"/>
+      <c r="J101" s="12"/>
+      <c r="K101" s="12"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>101</v>
       </c>
@@ -5144,7 +5897,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>108</v>
       </c>
@@ -5164,7 +5917,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>21</v>
       </c>
@@ -5184,7 +5937,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>86</v>
       </c>
@@ -5204,7 +5957,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="17"/>
@@ -5213,8 +5966,11 @@
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I106" s="2"/>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>0</v>
       </c>
@@ -5228,7 +5984,7 @@
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>1</v>
       </c>
@@ -5240,7 +5996,7 @@
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>2</v>
       </c>
@@ -5254,7 +6010,7 @@
       <c r="G109" s="3"/>
       <c r="H109" s="3"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>4</v>
       </c>
@@ -5268,7 +6024,7 @@
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>5</v>
       </c>
@@ -5282,7 +6038,7 @@
       <c r="G111" s="3"/>
       <c r="H111" s="3"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>6</v>
       </c>
@@ -5296,7 +6052,7 @@
       <c r="G112" s="3"/>
       <c r="H112" s="3"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>8</v>
       </c>
@@ -5308,7 +6064,7 @@
       <c r="G113" s="3"/>
       <c r="H113" s="3"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>5</v>
       </c>
@@ -5333,8 +6089,17 @@
       <c r="H114" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I114" t="s">
+        <v>141</v>
+      </c>
+      <c r="J114" t="s">
+        <v>142</v>
+      </c>
+      <c r="K114" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>131</v>
       </c>
@@ -5357,7 +6122,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>107</v>
       </c>
@@ -5379,8 +6144,19 @@
       <c r="H116" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I116" s="10">
+        <v>3</v>
+      </c>
+      <c r="J116" s="12">
+        <f>C116</f>
+        <v>0.89440334956518253</v>
+      </c>
+      <c r="K116" s="12">
+        <f>0.1*J116</f>
+        <v>8.9440334956518264E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>89</v>
       </c>
@@ -5402,8 +6178,11 @@
       <c r="H117" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I117" s="10"/>
+      <c r="J117" s="12"/>
+      <c r="K117" s="12"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>123</v>
       </c>
@@ -5425,8 +6204,11 @@
       <c r="H118" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I118" s="10"/>
+      <c r="J118" s="12"/>
+      <c r="K118" s="12"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>33</v>
       </c>
@@ -5448,8 +6230,19 @@
       <c r="H119" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I119" s="10">
+        <v>3</v>
+      </c>
+      <c r="J119" s="12">
+        <f t="shared" ref="J119:J122" si="6">C119</f>
+        <v>0.5473301234083312</v>
+      </c>
+      <c r="K119" s="12">
+        <f>0.1*J119</f>
+        <v>5.4733012340833123E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>99</v>
       </c>
@@ -5471,8 +6264,19 @@
       <c r="H120" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I120" s="10">
+        <v>3</v>
+      </c>
+      <c r="J120" s="12">
+        <f t="shared" si="6"/>
+        <v>12.942566664203866</v>
+      </c>
+      <c r="K120" s="12">
+        <f>0.1*J120</f>
+        <v>1.2942566664203867</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>109</v>
       </c>
@@ -5494,8 +6298,11 @@
       <c r="H121" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I121" s="10"/>
+      <c r="J121" s="12"/>
+      <c r="K121" s="12"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>37</v>
       </c>
@@ -5517,8 +6324,19 @@
       <c r="H122" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I122" s="10">
+        <v>3</v>
+      </c>
+      <c r="J122" s="12">
+        <f t="shared" si="6"/>
+        <v>0.28078564277733647</v>
+      </c>
+      <c r="K122" s="12">
+        <f>0.1*J122</f>
+        <v>2.8078564277733649E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>101</v>
       </c>
@@ -5538,7 +6356,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
         <v>21</v>
       </c>
@@ -5558,7 +6376,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
         <v>133</v>
       </c>
@@ -5578,7 +6396,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="17"/>
@@ -5587,8 +6405,11 @@
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I126" s="2"/>
+      <c r="J126" s="2"/>
+      <c r="K126" s="2"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>0</v>
       </c>
@@ -5602,7 +6423,7 @@
       <c r="G127" s="3"/>
       <c r="H127" s="3"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>1</v>
       </c>
@@ -5614,7 +6435,7 @@
       <c r="G128" s="3"/>
       <c r="H128" s="3"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>2</v>
       </c>
@@ -5628,7 +6449,7 @@
       <c r="G129" s="3"/>
       <c r="H129" s="3"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>4</v>
       </c>
@@ -5642,7 +6463,7 @@
       <c r="G130" s="3"/>
       <c r="H130" s="3"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>5</v>
       </c>
@@ -5656,7 +6477,7 @@
       <c r="G131" s="3"/>
       <c r="H131" s="3"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>6</v>
       </c>
@@ -5670,7 +6491,7 @@
       <c r="G132" s="3"/>
       <c r="H132" s="3"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>8</v>
       </c>
@@ -5682,7 +6503,7 @@
       <c r="G133" s="3"/>
       <c r="H133" s="3"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
         <v>5</v>
       </c>
@@ -5707,8 +6528,17 @@
       <c r="H134" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I134" t="s">
+        <v>141</v>
+      </c>
+      <c r="J134" t="s">
+        <v>142</v>
+      </c>
+      <c r="K134" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>132</v>
       </c>
@@ -5731,7 +6561,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>105</v>
       </c>
@@ -5753,8 +6583,19 @@
       <c r="H136" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I136" s="10">
+        <v>3</v>
+      </c>
+      <c r="J136" s="12">
+        <f>C136</f>
+        <v>0.89440334956518253</v>
+      </c>
+      <c r="K136" s="12">
+        <f>0.1*J136</f>
+        <v>8.9440334956518264E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>89</v>
       </c>
@@ -5776,8 +6617,11 @@
       <c r="H137" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I137" s="10"/>
+      <c r="J137" s="12"/>
+      <c r="K137" s="12"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>123</v>
       </c>
@@ -5799,8 +6643,11 @@
       <c r="H138" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I138" s="10"/>
+      <c r="J138" s="12"/>
+      <c r="K138" s="12"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>33</v>
       </c>
@@ -5822,8 +6669,19 @@
       <c r="H139" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I139" s="10">
+        <v>3</v>
+      </c>
+      <c r="J139" s="12">
+        <f t="shared" ref="J139:J142" si="7">C139</f>
+        <v>0.5473301234083312</v>
+      </c>
+      <c r="K139" s="12">
+        <f>0.1*J139</f>
+        <v>5.4733012340833123E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>99</v>
       </c>
@@ -5845,8 +6703,19 @@
       <c r="H140" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I140" s="10">
+        <v>3</v>
+      </c>
+      <c r="J140" s="12">
+        <f t="shared" si="7"/>
+        <v>12.942566664203866</v>
+      </c>
+      <c r="K140" s="12">
+        <f>0.1*J140</f>
+        <v>1.2942566664203867</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>109</v>
       </c>
@@ -5868,8 +6737,11 @@
       <c r="H141" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I141" s="10"/>
+      <c r="J141" s="12"/>
+      <c r="K141" s="12"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>37</v>
       </c>
@@ -5891,8 +6763,19 @@
       <c r="H142" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I142" s="10">
+        <v>3</v>
+      </c>
+      <c r="J142" s="12">
+        <f t="shared" si="7"/>
+        <v>0.28078564277733647</v>
+      </c>
+      <c r="K142" s="12">
+        <f>0.1*J142</f>
+        <v>2.8078564277733649E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
         <v>101</v>
       </c>
@@ -5912,7 +6795,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
         <v>21</v>
       </c>
@@ -5960,7 +6843,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C34B5634-5AF1-473B-AC78-6B82FA75D54C}">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.85546875" bestFit="1" customWidth="1"/>
@@ -5973,7 +6856,7 @@
     <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5987,7 +6870,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -5999,7 +6882,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -6013,7 +6896,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -6027,7 +6910,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -6041,7 +6924,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
@@ -6055,7 +6938,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -6067,7 +6950,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
@@ -6092,8 +6975,17 @@
       <c r="H8" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" t="s">
+        <v>141</v>
+      </c>
+      <c r="J8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -6116,7 +7008,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>114</v>
       </c>
@@ -6138,8 +7030,19 @@
       <c r="H10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="10">
+        <v>3</v>
+      </c>
+      <c r="J10" s="12">
+        <f>C10</f>
+        <v>6.5856585494280209E-2</v>
+      </c>
+      <c r="K10" s="12">
+        <f>0.1*J10</f>
+        <v>6.5856585494280216E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>112</v>
       </c>
@@ -6161,8 +7064,11 @@
       <c r="H11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="10"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>118</v>
       </c>
@@ -6184,8 +7090,11 @@
       <c r="H12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="10"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -6207,8 +7116,11 @@
       <c r="H13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="10"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>126</v>
       </c>
@@ -6230,8 +7142,11 @@
       <c r="H14" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="10"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -6253,8 +7168,19 @@
       <c r="H15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="10">
+        <v>3</v>
+      </c>
+      <c r="J15" s="12">
+        <f t="shared" ref="J11:J17" si="0">C15</f>
+        <v>8.8525186072921841E-2</v>
+      </c>
+      <c r="K15" s="12">
+        <f>0.1*J15</f>
+        <v>8.8525186072921837E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>99</v>
       </c>
@@ -6276,8 +7202,19 @@
       <c r="H16" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" s="10">
+        <v>3</v>
+      </c>
+      <c r="J16" s="12">
+        <f t="shared" si="0"/>
+        <v>2.8004251669216531</v>
+      </c>
+      <c r="K16" s="12">
+        <f>0.1*J16</f>
+        <v>0.28004251669216534</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
@@ -6299,8 +7236,19 @@
       <c r="H17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" s="10">
+        <v>3</v>
+      </c>
+      <c r="J17" s="12">
+        <f t="shared" si="0"/>
+        <v>1.9247124104337052</v>
+      </c>
+      <c r="K17" s="12">
+        <f>0.1*J17</f>
+        <v>0.19247124104337054</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>90</v>
       </c>
@@ -6319,8 +7267,11 @@
       <c r="H18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" s="10"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>116</v>
       </c>
@@ -6340,8 +7291,11 @@
       <c r="H19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" s="10"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>86</v>
       </c>
@@ -6361,8 +7315,11 @@
       <c r="H20" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" s="10"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="17"/>
@@ -6371,8 +7328,11 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -6386,7 +7346,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>1</v>
       </c>
@@ -6398,7 +7358,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>2</v>
       </c>
@@ -6412,7 +7372,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>4</v>
       </c>
@@ -6426,7 +7386,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>5</v>
       </c>
@@ -6440,7 +7400,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>6</v>
       </c>
@@ -6454,7 +7414,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>8</v>
       </c>
@@ -6466,7 +7426,7 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>5</v>
       </c>
@@ -6491,8 +7451,17 @@
       <c r="H29" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" t="s">
+        <v>141</v>
+      </c>
+      <c r="J29" t="s">
+        <v>142</v>
+      </c>
+      <c r="K29" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>120</v>
       </c>
@@ -6515,7 +7484,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>104</v>
       </c>
@@ -6537,8 +7506,19 @@
       <c r="H31" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="10">
+        <v>3</v>
+      </c>
+      <c r="J31" s="12">
+        <f>C31</f>
+        <v>6.5856585494280209E-2</v>
+      </c>
+      <c r="K31" s="12">
+        <f>0.1*J31</f>
+        <v>6.5856585494280216E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>112</v>
       </c>
@@ -6560,8 +7540,11 @@
       <c r="H32" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="10"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>118</v>
       </c>
@@ -6583,8 +7566,11 @@
       <c r="H33" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="10"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>89</v>
       </c>
@@ -6606,8 +7592,11 @@
       <c r="H34" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="10"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>126</v>
       </c>
@@ -6629,8 +7618,11 @@
       <c r="H35" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="10"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -6652,8 +7644,19 @@
       <c r="H36" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36" s="10">
+        <v>3</v>
+      </c>
+      <c r="J36" s="12">
+        <f t="shared" ref="J32:J38" si="1">C36</f>
+        <v>8.8525186072921841E-2</v>
+      </c>
+      <c r="K36" s="12">
+        <f>0.1*J36</f>
+        <v>8.8525186072921837E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>99</v>
       </c>
@@ -6675,8 +7678,19 @@
       <c r="H37" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37" s="10">
+        <v>3</v>
+      </c>
+      <c r="J37" s="12">
+        <f t="shared" si="1"/>
+        <v>2.8004251669216531</v>
+      </c>
+      <c r="K37" s="12">
+        <f>0.1*J37</f>
+        <v>0.28004251669216534</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
@@ -6698,8 +7712,19 @@
       <c r="H38" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38" s="10">
+        <v>3</v>
+      </c>
+      <c r="J38" s="12">
+        <f t="shared" si="1"/>
+        <v>1.9247124104337052</v>
+      </c>
+      <c r="K38" s="12">
+        <f>0.1*J38</f>
+        <v>0.19247124104337054</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>90</v>
       </c>
@@ -6718,8 +7743,11 @@
       <c r="H39" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" s="10"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>116</v>
       </c>
@@ -6739,8 +7767,11 @@
       <c r="H40" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" s="10"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>86</v>
       </c>
@@ -6760,6 +7791,9 @@
       <c r="H41" t="s">
         <v>19</v>
       </c>
+      <c r="I41" s="10"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6769,7 +7803,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{150773DC-8801-4506-8832-5BE54A26FACF}">
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.5703125" bestFit="1" customWidth="1"/>
@@ -6780,9 +7814,10 @@
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6796,7 +7831,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -6808,7 +7843,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -6822,7 +7857,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -6836,7 +7871,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -6850,7 +7885,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
@@ -6864,7 +7899,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -6876,7 +7911,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
@@ -6901,8 +7936,17 @@
       <c r="H8" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" t="s">
+        <v>141</v>
+      </c>
+      <c r="J8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>134</v>
       </c>
@@ -6925,7 +7969,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -6947,8 +7991,19 @@
       <c r="H10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="10">
+        <v>3</v>
+      </c>
+      <c r="J10" s="12">
+        <f>C10</f>
+        <v>0.82850000000000001</v>
+      </c>
+      <c r="K10" s="12">
+        <f>0.1*J10</f>
+        <v>8.2850000000000007E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>119</v>
       </c>
@@ -6970,8 +8025,19 @@
       <c r="H11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="10">
+        <v>3</v>
+      </c>
+      <c r="J11" s="12">
+        <f t="shared" ref="J11:J14" si="0">C11</f>
+        <v>0.4753</v>
+      </c>
+      <c r="K11" s="12">
+        <f>0.1*J11</f>
+        <v>4.7530000000000003E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -6993,8 +8059,11 @@
       <c r="H12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="10"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>99</v>
       </c>
@@ -7016,8 +8085,19 @@
       <c r="H13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="10">
+        <v>3</v>
+      </c>
+      <c r="J13" s="12">
+        <f t="shared" si="0"/>
+        <v>0.97905439999999999</v>
+      </c>
+      <c r="K13" s="12">
+        <f>0.1*J13</f>
+        <v>9.790544000000001E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
@@ -7039,8 +8119,19 @@
       <c r="H14" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="10">
+        <v>3</v>
+      </c>
+      <c r="J14" s="12">
+        <f t="shared" si="0"/>
+        <v>12.783581</v>
+      </c>
+      <c r="K14" s="12">
+        <f>0.1*J14</f>
+        <v>1.2783581000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>135</v>
       </c>
@@ -7059,8 +8150,9 @@
       <c r="H15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>108</v>
       </c>
@@ -7080,7 +8172,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>101</v>
       </c>
@@ -7100,7 +8192,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="17"/>
@@ -7109,8 +8201,11 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -7124,7 +8219,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>1</v>
       </c>
@@ -7136,7 +8231,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>2</v>
       </c>
@@ -7150,7 +8245,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>4</v>
       </c>
@@ -7164,7 +8259,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>5</v>
       </c>
@@ -7178,7 +8273,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>6</v>
       </c>
@@ -7192,7 +8287,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>8</v>
       </c>
@@ -7204,7 +8299,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>5</v>
       </c>
@@ -7229,8 +8324,17 @@
       <c r="H26" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" t="s">
+        <v>141</v>
+      </c>
+      <c r="J26" t="s">
+        <v>142</v>
+      </c>
+      <c r="K26" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>136</v>
       </c>
@@ -7253,7 +8357,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -7275,8 +8379,19 @@
       <c r="H28" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" s="10">
+        <v>3</v>
+      </c>
+      <c r="J28" s="12">
+        <f>C28</f>
+        <v>0.82850000000000001</v>
+      </c>
+      <c r="K28" s="12">
+        <f>0.1*J28</f>
+        <v>8.2850000000000007E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>122</v>
       </c>
@@ -7298,8 +8413,19 @@
       <c r="H29" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="10">
+        <v>3</v>
+      </c>
+      <c r="J29" s="12">
+        <f t="shared" ref="J29:J32" si="1">C29</f>
+        <v>0.4753</v>
+      </c>
+      <c r="K29" s="12">
+        <f>0.1*J29</f>
+        <v>4.7530000000000003E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -7321,8 +8447,11 @@
       <c r="H30" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="10"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>99</v>
       </c>
@@ -7344,8 +8473,19 @@
       <c r="H31" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="10">
+        <v>3</v>
+      </c>
+      <c r="J31" s="12">
+        <f t="shared" si="1"/>
+        <v>0.97905439999999999</v>
+      </c>
+      <c r="K31" s="12">
+        <f>0.1*J31</f>
+        <v>9.790544000000001E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
@@ -7367,8 +8507,19 @@
       <c r="H32" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="10">
+        <v>3</v>
+      </c>
+      <c r="J32" s="12">
+        <f t="shared" si="1"/>
+        <v>12.783581</v>
+      </c>
+      <c r="K32" s="12">
+        <f>0.1*J32</f>
+        <v>1.2783581000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>135</v>
       </c>
@@ -7388,7 +8539,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>108</v>
       </c>
@@ -7408,7 +8559,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>101</v>
       </c>
@@ -7428,7 +8579,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="17"/>
@@ -7437,8 +8588,11 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
@@ -7452,7 +8606,7 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>1</v>
       </c>
@@ -7464,7 +8618,7 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>2</v>
       </c>
@@ -7478,7 +8632,7 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>4</v>
       </c>
@@ -7492,7 +8646,7 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>5</v>
       </c>
@@ -7506,7 +8660,7 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>6</v>
       </c>
@@ -7520,7 +8674,7 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>8</v>
       </c>
@@ -7532,7 +8686,7 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>5</v>
       </c>
@@ -7557,8 +8711,17 @@
       <c r="H44" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44" t="s">
+        <v>141</v>
+      </c>
+      <c r="J44" t="s">
+        <v>142</v>
+      </c>
+      <c r="K44" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>137</v>
       </c>
@@ -7581,7 +8744,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>118</v>
       </c>
@@ -7603,8 +8766,19 @@
       <c r="H46" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I46" s="10">
+        <v>3</v>
+      </c>
+      <c r="J46" s="12">
+        <f>C46</f>
+        <v>0.92220000000000002</v>
+      </c>
+      <c r="K46" s="12">
+        <f>0.1*J46</f>
+        <v>9.222000000000001E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>121</v>
       </c>
@@ -7626,8 +8800,19 @@
       <c r="H47" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47" s="10">
+        <v>3</v>
+      </c>
+      <c r="J47" s="12">
+        <f t="shared" ref="J47:J50" si="2">C47</f>
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="K47" s="12">
+        <f>0.1*J47</f>
+        <v>4.7899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>33</v>
       </c>
@@ -7649,8 +8834,11 @@
       <c r="H48" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48" s="10"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>99</v>
       </c>
@@ -7672,8 +8860,19 @@
       <c r="H49" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I49" s="10">
+        <v>3</v>
+      </c>
+      <c r="J49" s="12">
+        <f t="shared" si="2"/>
+        <v>4.9474215120689138</v>
+      </c>
+      <c r="K49" s="12">
+        <f>0.1*J49</f>
+        <v>0.49474215120689141</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>37</v>
       </c>
@@ -7695,8 +8894,19 @@
       <c r="H50" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I50" s="10">
+        <v>3</v>
+      </c>
+      <c r="J50" s="12">
+        <f t="shared" si="2"/>
+        <v>6.9231678675119195</v>
+      </c>
+      <c r="K50" s="12">
+        <f>0.1*J50</f>
+        <v>0.69231678675119201</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -7718,8 +8928,11 @@
       <c r="H51" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I51" s="10"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="17"/>
@@ -7728,8 +8941,11 @@
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>0</v>
       </c>
@@ -7743,7 +8959,7 @@
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>1</v>
       </c>
@@ -7755,7 +8971,7 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>2</v>
       </c>
@@ -7769,7 +8985,7 @@
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>4</v>
       </c>
@@ -7783,7 +8999,7 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>5</v>
       </c>
@@ -7797,7 +9013,7 @@
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>6</v>
       </c>
@@ -7811,7 +9027,7 @@
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>8</v>
       </c>
@@ -7823,7 +9039,7 @@
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>5</v>
       </c>
@@ -7848,8 +9064,17 @@
       <c r="H60" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I60" t="s">
+        <v>141</v>
+      </c>
+      <c r="J60" t="s">
+        <v>142</v>
+      </c>
+      <c r="K60" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>138</v>
       </c>
@@ -7872,7 +9097,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>118</v>
       </c>
@@ -7894,8 +9119,19 @@
       <c r="H62" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I62" s="10">
+        <v>3</v>
+      </c>
+      <c r="J62" s="12">
+        <f>C62</f>
+        <v>0.92220000000000002</v>
+      </c>
+      <c r="K62" s="12">
+        <f>0.1*J62</f>
+        <v>9.222000000000001E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>120</v>
       </c>
@@ -7917,8 +9153,19 @@
       <c r="H63" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I63" s="10">
+        <v>3</v>
+      </c>
+      <c r="J63" s="12">
+        <f t="shared" ref="J63:J66" si="3">C63</f>
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="K63" s="12">
+        <f>0.1*J63</f>
+        <v>4.7899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>33</v>
       </c>
@@ -7940,8 +9187,11 @@
       <c r="H64" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I64" s="10"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="12"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>99</v>
       </c>
@@ -7963,8 +9213,19 @@
       <c r="H65" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I65" s="10">
+        <v>3</v>
+      </c>
+      <c r="J65" s="12">
+        <f t="shared" si="3"/>
+        <v>4.9474215120689138</v>
+      </c>
+      <c r="K65" s="12">
+        <f>0.1*J65</f>
+        <v>0.49474215120689141</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>37</v>
       </c>
@@ -7986,8 +9247,19 @@
       <c r="H66" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I66" s="10">
+        <v>3</v>
+      </c>
+      <c r="J66" s="12">
+        <f t="shared" si="3"/>
+        <v>6.9231678675119195</v>
+      </c>
+      <c r="K66" s="12">
+        <f>0.1*J66</f>
+        <v>0.69231678675119201</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>89</v>
       </c>
@@ -8009,6 +9281,9 @@
       <c r="H67" t="s">
         <v>16</v>
       </c>
+      <c r="I67" s="10"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/inventories_ei310_monte_carlo.xlsx
+++ b/data/inventories_ei310_monte_carlo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBF6600-3E81-4EF8-93F7-AFA4AFB67F0C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C344219C-7057-445A-97A6-5CBD9B9F5317}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" activeTab="3" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="hydrogen" sheetId="14" r:id="rId1"/>
@@ -7172,7 +7172,7 @@
         <v>3</v>
       </c>
       <c r="J15" s="12">
-        <f t="shared" ref="J11:J17" si="0">C15</f>
+        <f t="shared" ref="J15:J17" si="0">C15</f>
         <v>8.8525186072921841E-2</v>
       </c>
       <c r="K15" s="12">
@@ -7648,7 +7648,7 @@
         <v>3</v>
       </c>
       <c r="J36" s="12">
-        <f t="shared" ref="J32:J38" si="1">C36</f>
+        <f t="shared" ref="J36:J38" si="1">C36</f>
         <v>8.8525186072921841E-2</v>
       </c>
       <c r="K36" s="12">
